--- a/predictions/20260823/騎手運勢2026.08.22.xlsx
+++ b/predictions/20260823/騎手運勢2026.08.22.xlsx
@@ -420,7 +420,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -479,6 +479,24 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor rgb="FFFF7C80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +586,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -831,6 +849,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1152,12 +1188,12 @@
           <t>金星－</t>
         </is>
       </c>
-      <c r="B3" s="55" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="C3" s="55" t="inlineStr">
+      <c r="C3" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1176,12 +1212,12 @@
           <t>金星＋</t>
         </is>
       </c>
-      <c r="B4" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1198,12 +1234,12 @@
           <t>金星霊－</t>
         </is>
       </c>
-      <c r="B5" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="B5" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C5" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1220,12 +1256,12 @@
           <t>金星霊＋</t>
         </is>
       </c>
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C6" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1242,12 +1278,12 @@
           <t>木星－</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C7" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1266,12 +1302,12 @@
           <t>木星＋</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1290,12 +1326,12 @@
           <t>木星霊－</t>
         </is>
       </c>
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1308,12 +1344,12 @@
           <t>木星霊＋</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="B10" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1330,12 +1366,12 @@
           <t>水星－</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="inlineStr">
+      <c r="B11" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C11" s="90" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1353,12 +1389,12 @@
           <t>水星＋</t>
         </is>
       </c>
-      <c r="B12" s="57" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="B12" s="90" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1377,12 +1413,12 @@
           <t>水星霊－</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="B13" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1399,12 +1435,12 @@
           <t>水星霊＋</t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C14" s="83" t="inlineStr">
+      <c r="B14" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1417,12 +1453,12 @@
           <t>火星－</t>
         </is>
       </c>
-      <c r="B15" s="56" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C15" s="56" t="inlineStr">
+      <c r="B15" s="90" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1440,12 +1476,12 @@
           <t>火星＋</t>
         </is>
       </c>
-      <c r="B16" s="56" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C16" s="57" t="inlineStr">
+      <c r="B16" s="90" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1463,12 +1499,12 @@
           <t>火星霊－</t>
         </is>
       </c>
-      <c r="B17" s="56" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C17" s="56" t="inlineStr">
+      <c r="B17" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C17" s="93" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
@@ -1485,12 +1521,12 @@
           <t>火星霊＋</t>
         </is>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="93" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
       </c>
-      <c r="C18" s="56" t="inlineStr">
+      <c r="C18" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1507,12 +1543,12 @@
           <t>土星－</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="C19" s="55" t="inlineStr">
+      <c r="C19" s="93" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
@@ -1530,12 +1566,12 @@
           <t>土星＋</t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="93" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
       </c>
-      <c r="C20" s="55" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1555,12 +1591,12 @@
           <t>土星霊－</t>
         </is>
       </c>
-      <c r="B21" s="83" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="inlineStr">
+      <c r="B21" s="92" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C21" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1577,12 +1613,12 @@
           <t>土星霊＋</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C22" s="55" t="inlineStr">
+      <c r="B22" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C22" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1599,12 +1635,12 @@
           <t>天王星－</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
+      <c r="B23" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1623,12 +1659,12 @@
           <t>天王星＋</t>
         </is>
       </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C24" s="83" t="inlineStr">
+      <c r="B24" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C24" s="91" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1646,12 +1682,12 @@
           <t>天王星霊－</t>
         </is>
       </c>
-      <c r="B25" s="56" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="inlineStr">
+      <c r="B25" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1668,12 +1704,12 @@
           <t>天王星霊＋</t>
         </is>
       </c>
-      <c r="B26" s="56" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -10475,7 +10511,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -11266,7 +11302,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -12045,7 +12081,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -12860,7 +12896,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -13676,7 +13712,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
       <c r="F1" s="17" t="inlineStr">
         <is>
           <t>赤字：私の期待騎手、青字：回収率の高い穴騎手</t>
@@ -14497,7 +14533,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
       <c r="F1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -15325,7 +15361,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="88" t="n"/>
+      <c r="E1" s="94" t="n"/>
       <c r="F1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -16853,8 +16889,8 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="89" t="n"/>
-      <c r="F1" s="88" t="n"/>
+      <c r="E1" s="95" t="n"/>
+      <c r="F1" s="94" t="n"/>
       <c r="G1" s="26" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -21664,8 +21700,8 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="89" t="n"/>
-      <c r="F1" s="88" t="n"/>
+      <c r="E1" s="95" t="n"/>
+      <c r="F1" s="94" t="n"/>
       <c r="G1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い調教師</t>

--- a/predictions/20260823/騎手運勢2026.08.22.xlsx
+++ b/predictions/20260823/騎手運勢2026.08.22.xlsx
@@ -420,7 +420,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -479,24 +479,6 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-        <bgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF7C80"/>
-        <bgColor rgb="FFFF7C80"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -586,7 +568,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,22 +831,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1188,12 +1158,12 @@
           <t>金星－</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="C3" s="89" t="inlineStr">
+      <c r="C3" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1212,12 +1182,12 @@
           <t>金星＋</t>
         </is>
       </c>
-      <c r="B4" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C4" s="90" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" s="57" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1234,12 +1204,12 @@
           <t>金星霊－</t>
         </is>
       </c>
-      <c r="B5" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C5" s="89" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1256,12 +1226,12 @@
           <t>金星霊＋</t>
         </is>
       </c>
-      <c r="B6" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C6" s="89" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1278,12 +1248,12 @@
           <t>木星－</t>
         </is>
       </c>
-      <c r="B7" s="91" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C7" s="89" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1302,12 +1272,12 @@
           <t>木星＋</t>
         </is>
       </c>
-      <c r="B8" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C8" s="89" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1326,12 +1296,12 @@
           <t>木星霊－</t>
         </is>
       </c>
-      <c r="B9" s="88" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C9" s="89" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1344,12 +1314,12 @@
           <t>木星霊＋</t>
         </is>
       </c>
-      <c r="B10" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C10" s="89" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1366,12 +1336,12 @@
           <t>水星－</t>
         </is>
       </c>
-      <c r="B11" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C11" s="90" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1389,12 +1359,12 @@
           <t>水星＋</t>
         </is>
       </c>
-      <c r="B12" s="90" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C12" s="88" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1413,12 +1383,12 @@
           <t>水星霊－</t>
         </is>
       </c>
-      <c r="B13" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C13" s="89" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1435,12 +1405,12 @@
           <t>水星霊＋</t>
         </is>
       </c>
-      <c r="B14" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C14" s="92" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1453,12 +1423,12 @@
           <t>火星－</t>
         </is>
       </c>
-      <c r="B15" s="90" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C15" s="90" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
@@ -1476,12 +1446,12 @@
           <t>火星＋</t>
         </is>
       </c>
-      <c r="B16" s="90" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1499,12 +1469,12 @@
           <t>火星霊－</t>
         </is>
       </c>
-      <c r="B17" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C17" s="93" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
@@ -1521,12 +1491,12 @@
           <t>火星霊＋</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
+      <c r="B18" s="52" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1543,12 +1513,12 @@
           <t>土星－</t>
         </is>
       </c>
-      <c r="B19" s="88" t="inlineStr">
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="C19" s="93" t="inlineStr">
+      <c r="C19" s="52" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
@@ -1566,12 +1536,12 @@
           <t>土星＋</t>
         </is>
       </c>
-      <c r="B20" s="93" t="inlineStr">
+      <c r="B20" s="52" t="inlineStr">
         <is>
           <t>◎◎</t>
         </is>
       </c>
-      <c r="C20" s="88" t="inlineStr">
+      <c r="C20" s="53" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1591,12 +1561,12 @@
           <t>土星霊－</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C21" s="89" t="inlineStr">
+      <c r="B21" s="89" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1613,12 +1583,12 @@
           <t>土星霊＋</t>
         </is>
       </c>
-      <c r="B22" s="89" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C22" s="89" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -1635,12 +1605,12 @@
           <t>天王星－</t>
         </is>
       </c>
-      <c r="B23" s="88" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C23" s="88" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1659,12 +1629,12 @@
           <t>天王星＋</t>
         </is>
       </c>
-      <c r="B24" s="88" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C24" s="91" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1682,12 +1652,12 @@
           <t>天王星霊－</t>
         </is>
       </c>
-      <c r="B25" s="88" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C25" s="88" t="inlineStr">
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1704,12 +1674,12 @@
           <t>天王星霊＋</t>
         </is>
       </c>
-      <c r="B26" s="88" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C26" s="88" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -10511,7 +10481,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -11302,7 +11272,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -12081,7 +12051,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -12896,7 +12866,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="87">
       <c r="A2" s="2" t="n"/>
@@ -13712,7 +13682,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
       <c r="F1" s="17" t="inlineStr">
         <is>
           <t>赤字：私の期待騎手、青字：回収率の高い穴騎手</t>
@@ -14533,7 +14503,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
       <c r="F1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -15361,7 +15331,7 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="94" t="n"/>
+      <c r="E1" s="90" t="n"/>
       <c r="F1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -16889,8 +16859,8 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="95" t="n"/>
-      <c r="F1" s="94" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="90" t="n"/>
       <c r="G1" s="26" t="inlineStr">
         <is>
           <t>青字：回収率の高い騎手（100％以上）</t>
@@ -21700,8 +21670,8 @@
           <t>日運</t>
         </is>
       </c>
-      <c r="E1" s="95" t="n"/>
-      <c r="F1" s="94" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="90" t="n"/>
       <c r="G1" s="18" t="inlineStr">
         <is>
           <t>青字：回収率の高い調教師</t>
